--- a/data/trans_orig/P6713-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P6713-Habitat-trans_orig.xlsx
@@ -536,7 +536,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si su trabajo le permite que aprenda cosas nuevas en 2012</t>
+          <t>Población según si su trabajo le permite que aprenda cosas nuevas en 2012 (tasa de respuesta: 99,1%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -731,12 +731,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1041</t>
+          <t>1047</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>10378</t>
+          <t>10187</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -751,7 +751,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,86%</t>
+          <t>3,79%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -766,12 +766,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>2891</t>
+          <t>2887</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>13152</t>
+          <t>12712</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -786,7 +786,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>8,15%</t>
+          <t>7,88%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -801,12 +801,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>5862</t>
+          <t>5839</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>18540</t>
+          <t>18639</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -821,7 +821,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,31%</t>
+          <t>4,33%</t>
         </is>
       </c>
     </row>
@@ -844,12 +844,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>7638</t>
+          <t>7774</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>26070</t>
+          <t>25274</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -859,12 +859,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>2,89%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>9,69%</t>
+          <t>9,4%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -879,12 +879,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>4124</t>
+          <t>4233</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>17168</t>
+          <t>17131</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -894,12 +894,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,62%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>10,65%</t>
+          <t>10,62%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -914,12 +914,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>14460</t>
+          <t>14902</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>34802</t>
+          <t>36983</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -929,12 +929,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>3,46%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>8,09%</t>
+          <t>8,6%</t>
         </is>
       </c>
     </row>
@@ -957,12 +957,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>37249</t>
+          <t>37451</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>62007</t>
+          <t>61871</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -972,12 +972,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>13,85%</t>
+          <t>13,93%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>23,06%</t>
+          <t>23,01%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>24874</t>
+          <t>25423</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>47228</t>
+          <t>47136</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>15,42%</t>
+          <t>15,76%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>29,28%</t>
+          <t>29,23%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>68784</t>
+          <t>68494</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>101875</t>
+          <t>102594</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1042,12 +1042,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>15,99%</t>
+          <t>15,92%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>23,68%</t>
+          <t>23,85%</t>
         </is>
       </c>
     </row>
@@ -1070,12 +1070,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>49172</t>
+          <t>48611</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>78713</t>
+          <t>77376</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1085,12 +1085,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>18,28%</t>
+          <t>18,08%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>29,27%</t>
+          <t>28,77%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1105,12 +1105,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>32349</t>
+          <t>33638</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>56054</t>
+          <t>56868</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1120,12 +1120,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>20,06%</t>
+          <t>20,86%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>34,76%</t>
+          <t>35,26%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1140,12 +1140,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>87690</t>
+          <t>87754</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>125113</t>
+          <t>124750</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1155,12 +1155,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>20,38%</t>
+          <t>20,4%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>29,08%</t>
+          <t>29,0%</t>
         </is>
       </c>
     </row>
@@ -1183,12 +1183,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>124602</t>
+          <t>122223</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>156134</t>
+          <t>156273</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1198,12 +1198,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>46,33%</t>
+          <t>45,45%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>58,06%</t>
+          <t>58,11%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1218,12 +1218,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>54777</t>
+          <t>52198</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>80708</t>
+          <t>78180</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1233,12 +1233,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>33,96%</t>
+          <t>32,37%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>50,04%</t>
+          <t>48,48%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1253,12 +1253,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>183917</t>
+          <t>185526</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>226921</t>
+          <t>227004</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1268,12 +1268,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>42,75%</t>
+          <t>43,12%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>52,75%</t>
+          <t>52,77%</t>
         </is>
       </c>
     </row>
@@ -1413,12 +1413,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>13471</t>
+          <t>14107</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>34191</t>
+          <t>33678</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1428,12 +1428,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>3,45%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>8,37%</t>
+          <t>8,24%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1448,12 +1448,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>11303</t>
+          <t>11470</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>29193</t>
+          <t>28521</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1463,12 +1463,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>4,26%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>10,84%</t>
+          <t>10,6%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1483,12 +1483,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>28611</t>
+          <t>30024</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>54149</t>
+          <t>55202</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1498,12 +1498,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,22%</t>
+          <t>4,43%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>7,99%</t>
+          <t>8,14%</t>
         </is>
       </c>
     </row>
@@ -1526,12 +1526,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>14733</t>
+          <t>14977</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>34675</t>
+          <t>36179</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1541,12 +1541,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>3,67%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>8,49%</t>
+          <t>8,85%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1561,12 +1561,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>13821</t>
+          <t>13235</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>32434</t>
+          <t>30520</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1576,12 +1576,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>5,13%</t>
+          <t>4,92%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>12,05%</t>
+          <t>11,34%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1596,12 +1596,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>33596</t>
+          <t>32577</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>60643</t>
+          <t>59753</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1611,12 +1611,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>4,96%</t>
+          <t>4,81%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>8,95%</t>
+          <t>8,82%</t>
         </is>
       </c>
     </row>
@@ -1639,12 +1639,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>60717</t>
+          <t>62629</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>94491</t>
+          <t>94079</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1654,12 +1654,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>14,86%</t>
+          <t>15,33%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>23,13%</t>
+          <t>23,02%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1674,12 +1674,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>41138</t>
+          <t>40802</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>69604</t>
+          <t>68357</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1689,12 +1689,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>15,28%</t>
+          <t>15,16%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>25,86%</t>
+          <t>25,39%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1709,12 +1709,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>111781</t>
+          <t>112619</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>154012</t>
+          <t>153365</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1724,12 +1724,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>16,49%</t>
+          <t>16,62%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>22,72%</t>
+          <t>22,63%</t>
         </is>
       </c>
     </row>
@@ -1752,12 +1752,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>77100</t>
+          <t>77480</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>114611</t>
+          <t>114153</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1767,12 +1767,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>18,87%</t>
+          <t>18,96%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>28,05%</t>
+          <t>27,94%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1787,12 +1787,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>44399</t>
+          <t>44896</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>72787</t>
+          <t>72596</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1802,12 +1802,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>16,49%</t>
+          <t>16,68%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>27,04%</t>
+          <t>26,97%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1822,12 +1822,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>132123</t>
+          <t>131541</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>177406</t>
+          <t>176419</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1837,12 +1837,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>19,49%</t>
+          <t>19,41%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>26,17%</t>
+          <t>26,03%</t>
         </is>
       </c>
     </row>
@@ -1865,12 +1865,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>169656</t>
+          <t>170410</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>210723</t>
+          <t>212874</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1880,12 +1880,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>41,52%</t>
+          <t>41,71%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>51,57%</t>
+          <t>52,1%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1900,12 +1900,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>99521</t>
+          <t>100916</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>134713</t>
+          <t>133161</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1915,12 +1915,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>36,97%</t>
+          <t>37,49%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>50,04%</t>
+          <t>49,47%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1935,12 +1935,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>283794</t>
+          <t>282329</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>336132</t>
+          <t>335263</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1950,12 +1950,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>41,87%</t>
+          <t>41,65%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>49,59%</t>
+          <t>49,46%</t>
         </is>
       </c>
     </row>
@@ -2095,12 +2095,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>7111</t>
+          <t>7053</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>21885</t>
+          <t>21908</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2110,12 +2110,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>6,83%</t>
+          <t>6,84%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2130,12 +2130,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>12551</t>
+          <t>12328</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>30504</t>
+          <t>31929</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2145,12 +2145,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>5,88%</t>
+          <t>5,78%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
+          <t>14,97%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2165,12 +2165,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>23969</t>
+          <t>23611</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>48992</t>
+          <t>48054</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>4,49%</t>
+          <t>4,42%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>9,18%</t>
+          <t>9,0%</t>
         </is>
       </c>
     </row>
@@ -2208,12 +2208,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>12956</t>
+          <t>13196</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>31779</t>
+          <t>33067</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2223,12 +2223,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>4,04%</t>
+          <t>4,12%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>9,92%</t>
+          <t>10,32%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2243,12 +2243,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>7400</t>
+          <t>7618</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>24808</t>
+          <t>24183</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2258,12 +2258,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>3,57%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>11,63%</t>
+          <t>11,33%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2278,12 +2278,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>25129</t>
+          <t>24216</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>49093</t>
+          <t>50415</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2293,12 +2293,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>4,71%</t>
+          <t>4,54%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>9,2%</t>
+          <t>9,44%</t>
         </is>
       </c>
     </row>
@@ -2321,12 +2321,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>52882</t>
+          <t>53340</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>86146</t>
+          <t>84155</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2336,12 +2336,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>16,5%</t>
+          <t>16,64%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>26,88%</t>
+          <t>26,26%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2356,12 +2356,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>31251</t>
+          <t>29819</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>55293</t>
+          <t>55087</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2371,12 +2371,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>14,65%</t>
+          <t>13,98%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>25,92%</t>
+          <t>25,82%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2391,12 +2391,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>89934</t>
+          <t>91182</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>128768</t>
+          <t>129580</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2406,12 +2406,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>16,85%</t>
+          <t>17,08%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>24,12%</t>
+          <t>24,27%</t>
         </is>
       </c>
     </row>
@@ -2434,12 +2434,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>39743</t>
+          <t>39398</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>68368</t>
+          <t>67524</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>12,4%</t>
+          <t>12,29%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>21,33%</t>
+          <t>21,07%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2469,12 +2469,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>24721</t>
+          <t>23771</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>48969</t>
+          <t>46413</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2484,12 +2484,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>11,59%</t>
+          <t>11,14%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>22,95%</t>
+          <t>21,75%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2504,12 +2504,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>69803</t>
+          <t>69626</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>104298</t>
+          <t>106098</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2519,12 +2519,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>13,08%</t>
+          <t>13,04%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>19,54%</t>
+          <t>19,87%</t>
         </is>
       </c>
     </row>
@@ -2547,12 +2547,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>148013</t>
+          <t>147223</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>184026</t>
+          <t>183461</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2562,12 +2562,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>46,18%</t>
+          <t>45,94%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>57,42%</t>
+          <t>57,25%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2582,12 +2582,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>85960</t>
+          <t>86820</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>117070</t>
+          <t>116044</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2597,12 +2597,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>40,29%</t>
+          <t>40,69%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>54,87%</t>
+          <t>54,39%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2617,12 +2617,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>244188</t>
+          <t>241760</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>291026</t>
+          <t>293405</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2632,12 +2632,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>45,74%</t>
+          <t>45,29%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>54,52%</t>
+          <t>54,96%</t>
         </is>
       </c>
     </row>
@@ -2777,12 +2777,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>11615</t>
+          <t>12193</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>31138</t>
+          <t>29747</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2792,12 +2792,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>2,93%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>7,48%</t>
+          <t>7,14%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2812,12 +2812,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>8227</t>
+          <t>8075</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>22888</t>
+          <t>22253</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2827,12 +2827,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>7,62%</t>
+          <t>7,41%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2847,12 +2847,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>23680</t>
+          <t>23580</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>47830</t>
+          <t>48191</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>3,29%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>6,67%</t>
+          <t>6,72%</t>
         </is>
       </c>
     </row>
@@ -2890,12 +2890,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>9948</t>
+          <t>9984</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>26459</t>
+          <t>26849</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2905,12 +2905,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>6,35%</t>
+          <t>6,45%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2925,12 +2925,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>11031</t>
+          <t>11278</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>29137</t>
+          <t>28923</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2940,12 +2940,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>3,75%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>9,7%</t>
+          <t>9,63%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2960,12 +2960,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>25133</t>
+          <t>24567</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>48044</t>
+          <t>48929</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2975,12 +2975,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>3,51%</t>
+          <t>3,43%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>6,7%</t>
+          <t>6,83%</t>
         </is>
       </c>
     </row>
@@ -3003,12 +3003,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>77715</t>
+          <t>79120</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>113027</t>
+          <t>113734</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3018,12 +3018,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>18,66%</t>
+          <t>19,0%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>27,14%</t>
+          <t>27,31%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3038,12 +3038,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>53044</t>
+          <t>52730</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>84504</t>
+          <t>82479</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3053,12 +3053,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>17,65%</t>
+          <t>17,55%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>28,13%</t>
+          <t>27,45%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3073,12 +3073,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>141274</t>
+          <t>138099</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>187970</t>
+          <t>184973</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3088,12 +3088,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>19,71%</t>
+          <t>19,26%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>26,22%</t>
+          <t>25,8%</t>
         </is>
       </c>
     </row>
@@ -3116,12 +3116,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>96707</t>
+          <t>98364</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>132964</t>
+          <t>135511</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3131,12 +3131,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>23,22%</t>
+          <t>23,62%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>31,93%</t>
+          <t>32,54%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3151,12 +3151,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>49368</t>
+          <t>50075</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>78705</t>
+          <t>80689</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3166,12 +3166,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>16,43%</t>
+          <t>16,67%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>26,2%</t>
+          <t>26,86%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3186,12 +3186,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>158133</t>
+          <t>157566</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>205111</t>
+          <t>204564</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3201,12 +3201,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>22,06%</t>
+          <t>21,98%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>28,61%</t>
+          <t>28,54%</t>
         </is>
       </c>
     </row>
@@ -3229,12 +3229,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>148678</t>
+          <t>149311</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>191066</t>
+          <t>190893</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3244,12 +3244,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>35,7%</t>
+          <t>35,86%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>45,88%</t>
+          <t>45,84%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3264,12 +3264,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>121615</t>
+          <t>120414</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>155999</t>
+          <t>155817</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3279,12 +3279,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>40,48%</t>
+          <t>40,08%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>51,92%</t>
+          <t>51,86%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3299,12 +3299,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>280808</t>
+          <t>282097</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>334887</t>
+          <t>332850</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3314,12 +3314,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>39,17%</t>
+          <t>39,35%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>46,71%</t>
+          <t>46,43%</t>
         </is>
       </c>
     </row>
@@ -3459,12 +3459,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>44688</t>
+          <t>44843</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>76863</t>
+          <t>76887</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3474,12 +3474,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>3,17%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>5,43%</t>
+          <t>5,44%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3494,12 +3494,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>45780</t>
+          <t>46453</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>77034</t>
+          <t>76194</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3509,12 +3509,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>4,85%</t>
+          <t>4,92%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>8,16%</t>
+          <t>8,07%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3529,12 +3529,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>99351</t>
+          <t>96706</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>142515</t>
+          <t>139908</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3544,12 +3544,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>4,21%</t>
+          <t>4,1%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>6,04%</t>
+          <t>5,93%</t>
         </is>
       </c>
     </row>
@@ -3572,12 +3572,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>57682</t>
+          <t>59406</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>95795</t>
+          <t>95850</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3587,12 +3587,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>4,08%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>6,77%</t>
+          <t>6,78%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3607,12 +3607,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>48996</t>
+          <t>49205</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>83273</t>
+          <t>80445</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3622,12 +3622,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>5,19%</t>
+          <t>5,21%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>8,82%</t>
+          <t>8,52%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3642,12 +3642,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>116612</t>
+          <t>114879</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>166829</t>
+          <t>164835</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3657,12 +3657,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>4,94%</t>
+          <t>4,87%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>7,07%</t>
+          <t>6,99%</t>
         </is>
       </c>
     </row>
@@ -3685,12 +3685,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>258688</t>
+          <t>259390</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>324586</t>
+          <t>319812</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3700,12 +3700,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>18,29%</t>
+          <t>18,34%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>22,95%</t>
+          <t>22,61%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3720,12 +3720,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>173078</t>
+          <t>173678</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>225076</t>
+          <t>224700</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3735,12 +3735,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>18,33%</t>
+          <t>18,39%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>23,84%</t>
+          <t>23,8%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3755,12 +3755,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>448801</t>
+          <t>449396</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>532615</t>
+          <t>530917</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3770,12 +3770,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>19,03%</t>
+          <t>19,05%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>22,58%</t>
+          <t>22,51%</t>
         </is>
       </c>
     </row>
@@ -3798,12 +3798,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>293788</t>
+          <t>290681</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>358025</t>
+          <t>357649</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3813,12 +3813,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>20,77%</t>
+          <t>20,55%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>25,31%</t>
+          <t>25,29%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3833,12 +3833,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>173066</t>
+          <t>173052</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>223797</t>
+          <t>226030</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3853,7 +3853,7 @@
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>23,7%</t>
+          <t>23,94%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3868,12 +3868,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>480259</t>
+          <t>482769</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>567195</t>
+          <t>562307</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3883,12 +3883,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>20,36%</t>
+          <t>20,47%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>24,05%</t>
+          <t>23,84%</t>
         </is>
       </c>
     </row>
@@ -3911,12 +3911,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>628332</t>
+          <t>629882</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>706236</t>
+          <t>707062</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3926,12 +3926,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>44,42%</t>
+          <t>44,53%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>49,93%</t>
+          <t>49,99%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3946,12 +3946,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>391805</t>
+          <t>392031</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>456934</t>
+          <t>455033</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3961,12 +3961,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>41,49%</t>
+          <t>41,52%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>48,39%</t>
+          <t>48,19%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3981,12 +3981,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>1041204</t>
+          <t>1040461</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>1136814</t>
+          <t>1144728</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3996,12 +3996,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>44,14%</t>
+          <t>44,11%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>48,2%</t>
+          <t>48,53%</t>
         </is>
       </c>
     </row>
@@ -4178,7 +4178,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si su trabajo le permite que aprenda cosas nuevas en 2016</t>
+          <t>Población según si su trabajo le permite que aprenda cosas nuevas en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4373,12 +4373,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>8766</t>
+          <t>8953</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>24681</t>
+          <t>24515</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4388,12 +4388,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>3,68%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>10,14%</t>
+          <t>10,08%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4408,12 +4408,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>11588</t>
+          <t>10835</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>26795</t>
+          <t>26848</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4423,12 +4423,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>6,92%</t>
+          <t>6,47%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>16,01%</t>
+          <t>16,04%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4443,12 +4443,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>23557</t>
+          <t>21432</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>45195</t>
+          <t>44148</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4458,12 +4458,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>5,74%</t>
+          <t>5,22%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>11,01%</t>
+          <t>10,75%</t>
         </is>
       </c>
     </row>
@@ -4486,12 +4486,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>21211</t>
+          <t>21451</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>43171</t>
+          <t>41757</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4501,12 +4501,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>8,72%</t>
+          <t>8,82%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>17,74%</t>
+          <t>17,16%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4521,12 +4521,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>20893</t>
+          <t>20007</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>39030</t>
+          <t>40395</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4536,12 +4536,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>12,48%</t>
+          <t>11,95%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>23,32%</t>
+          <t>24,14%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4556,12 +4556,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>46702</t>
+          <t>46237</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>75538</t>
+          <t>76409</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4571,12 +4571,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>11,37%</t>
+          <t>11,26%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>18,39%</t>
+          <t>18,61%</t>
         </is>
       </c>
     </row>
@@ -4599,12 +4599,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>47959</t>
+          <t>47138</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>75109</t>
+          <t>74420</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4614,12 +4614,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>19,71%</t>
+          <t>19,38%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>30,87%</t>
+          <t>30,59%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -4634,12 +4634,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>24450</t>
+          <t>23931</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>43849</t>
+          <t>42958</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4649,12 +4649,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>14,61%</t>
+          <t>14,3%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>26,2%</t>
+          <t>25,67%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -4669,12 +4669,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>76735</t>
+          <t>78388</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>109676</t>
+          <t>109687</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4684,7 +4684,7 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>18,69%</t>
+          <t>19,09%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
@@ -4712,12 +4712,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>47853</t>
+          <t>47680</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>74520</t>
+          <t>75077</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4727,12 +4727,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>19,67%</t>
+          <t>19,6%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>30,63%</t>
+          <t>30,86%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4747,12 +4747,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>36855</t>
+          <t>37068</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>60118</t>
+          <t>60355</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4762,12 +4762,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>22,02%</t>
+          <t>22,15%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>35,92%</t>
+          <t>36,06%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4782,12 +4782,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>91804</t>
+          <t>91914</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>127658</t>
+          <t>127807</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4797,12 +4797,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>22,36%</t>
+          <t>22,38%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>31,09%</t>
+          <t>31,12%</t>
         </is>
       </c>
     </row>
@@ -4825,12 +4825,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>61227</t>
+          <t>63137</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>91778</t>
+          <t>92317</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4840,12 +4840,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>25,17%</t>
+          <t>25,95%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>37,72%</t>
+          <t>37,95%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4860,12 +4860,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>29880</t>
+          <t>29326</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>51664</t>
+          <t>51855</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4875,12 +4875,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>17,85%</t>
+          <t>17,52%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>30,87%</t>
+          <t>30,98%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4895,12 +4895,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>97636</t>
+          <t>98394</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>135047</t>
+          <t>135133</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4910,12 +4910,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>23,78%</t>
+          <t>23,96%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>32,89%</t>
+          <t>32,91%</t>
         </is>
       </c>
     </row>
@@ -5055,12 +5055,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>8157</t>
+          <t>8755</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>25460</t>
+          <t>25881</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5070,12 +5070,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>6,15%</t>
+          <t>6,25%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5090,12 +5090,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>14851</t>
+          <t>14402</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>33295</t>
+          <t>33870</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5105,12 +5105,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>5,42%</t>
+          <t>5,26%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>12,16%</t>
+          <t>12,37%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5125,12 +5125,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>26699</t>
+          <t>26645</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>51998</t>
+          <t>51844</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5140,12 +5140,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>3,87%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>7,56%</t>
+          <t>7,54%</t>
         </is>
       </c>
     </row>
@@ -5168,12 +5168,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>24089</t>
+          <t>23047</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>46891</t>
+          <t>45633</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5183,12 +5183,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>5,82%</t>
+          <t>5,57%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>11,33%</t>
+          <t>11,02%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5203,12 +5203,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>22225</t>
+          <t>21289</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>42073</t>
+          <t>42402</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5218,12 +5218,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>8,12%</t>
+          <t>7,78%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>15,37%</t>
+          <t>15,49%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5238,12 +5238,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>50406</t>
+          <t>51252</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>80736</t>
+          <t>82266</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5253,12 +5253,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>7,33%</t>
+          <t>7,45%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>11,74%</t>
+          <t>11,96%</t>
         </is>
       </c>
     </row>
@@ -5281,12 +5281,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>88729</t>
+          <t>87652</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>127613</t>
+          <t>125628</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5296,12 +5296,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>21,43%</t>
+          <t>21,17%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>30,82%</t>
+          <t>30,34%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5316,12 +5316,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>48990</t>
+          <t>47567</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>75038</t>
+          <t>75429</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5331,12 +5331,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>17,89%</t>
+          <t>17,37%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>27,41%</t>
+          <t>27,55%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -5351,12 +5351,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>144584</t>
+          <t>145859</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>191458</t>
+          <t>193565</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5366,12 +5366,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>21,02%</t>
+          <t>21,21%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>27,84%</t>
+          <t>28,14%</t>
         </is>
       </c>
     </row>
@@ -5394,12 +5394,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>102223</t>
+          <t>100646</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>142451</t>
+          <t>140855</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5409,12 +5409,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>24,69%</t>
+          <t>24,31%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>34,41%</t>
+          <t>34,02%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5429,12 +5429,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>64871</t>
+          <t>66461</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>94736</t>
+          <t>96740</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5444,12 +5444,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>23,7%</t>
+          <t>24,28%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>34,6%</t>
+          <t>35,34%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5464,12 +5464,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>179412</t>
+          <t>176346</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>226518</t>
+          <t>226903</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5479,12 +5479,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>26,08%</t>
+          <t>25,64%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>32,93%</t>
+          <t>32,99%</t>
         </is>
       </c>
     </row>
@@ -5507,12 +5507,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>118317</t>
+          <t>119261</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>159123</t>
+          <t>159295</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5522,12 +5522,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>28,58%</t>
+          <t>28,8%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>38,43%</t>
+          <t>38,47%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5542,12 +5542,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>65641</t>
+          <t>63371</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>95689</t>
+          <t>94874</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5557,12 +5557,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>23,98%</t>
+          <t>23,15%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>34,95%</t>
+          <t>34,65%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5577,12 +5577,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>192241</t>
+          <t>192186</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>240638</t>
+          <t>241877</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5592,12 +5592,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>27,95%</t>
+          <t>27,94%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>34,99%</t>
+          <t>35,17%</t>
         </is>
       </c>
     </row>
@@ -5737,12 +5737,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>15934</t>
+          <t>16102</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>35367</t>
+          <t>34982</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5752,12 +5752,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>4,38%</t>
+          <t>4,43%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>9,72%</t>
+          <t>9,62%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5772,12 +5772,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>10165</t>
+          <t>10506</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>27408</t>
+          <t>27592</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5787,12 +5787,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>3,88%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>10,13%</t>
+          <t>10,2%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5807,12 +5807,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>29997</t>
+          <t>28979</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>57006</t>
+          <t>56522</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5822,12 +5822,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>4,73%</t>
+          <t>4,57%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>8,99%</t>
+          <t>8,91%</t>
         </is>
       </c>
     </row>
@@ -5850,12 +5850,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>29402</t>
+          <t>29382</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>55126</t>
+          <t>55072</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5870,7 +5870,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>15,15%</t>
+          <t>15,14%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>26119</t>
+          <t>26099</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>47540</t>
+          <t>48920</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5905,7 +5905,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>17,57%</t>
+          <t>18,08%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5920,12 +5920,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>60542</t>
+          <t>61198</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>94636</t>
+          <t>95609</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5935,12 +5935,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>9,54%</t>
+          <t>9,65%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>14,92%</t>
+          <t>15,07%</t>
         </is>
       </c>
     </row>
@@ -5963,12 +5963,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>97725</t>
+          <t>97295</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>135230</t>
+          <t>135516</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5978,12 +5978,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>26,86%</t>
+          <t>26,74%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>37,17%</t>
+          <t>37,25%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -5998,12 +5998,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>70357</t>
+          <t>70743</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>101967</t>
+          <t>102051</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6013,12 +6013,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>26,0%</t>
+          <t>26,15%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>37,69%</t>
+          <t>37,72%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>177275</t>
+          <t>177654</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>225468</t>
+          <t>226897</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6048,12 +6048,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>27,94%</t>
+          <t>28,0%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>35,54%</t>
+          <t>35,77%</t>
         </is>
       </c>
     </row>
@@ -6076,12 +6076,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>62126</t>
+          <t>62151</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>95405</t>
+          <t>94798</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -6096,7 +6096,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>26,22%</t>
+          <t>26,06%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -6111,12 +6111,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>45565</t>
+          <t>44872</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>72695</t>
+          <t>71022</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -6126,12 +6126,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>16,84%</t>
+          <t>16,58%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>26,87%</t>
+          <t>26,25%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -6146,12 +6146,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>115694</t>
+          <t>115257</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>156288</t>
+          <t>156684</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -6161,12 +6161,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>18,24%</t>
+          <t>18,17%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>24,64%</t>
+          <t>24,7%</t>
         </is>
       </c>
     </row>
@@ -6189,12 +6189,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>88162</t>
+          <t>87471</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>122251</t>
+          <t>122796</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -6204,12 +6204,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>24,23%</t>
+          <t>24,04%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>33,6%</t>
+          <t>33,75%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -6224,12 +6224,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>60425</t>
+          <t>59435</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>88758</t>
+          <t>88094</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -6239,12 +6239,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>22,33%</t>
+          <t>21,97%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>32,81%</t>
+          <t>32,56%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -6259,12 +6259,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>156259</t>
+          <t>155971</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>202072</t>
+          <t>202033</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6274,7 +6274,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>24,63%</t>
+          <t>24,59%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -6419,12 +6419,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>16946</t>
+          <t>17742</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>38206</t>
+          <t>37746</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6434,12 +6434,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>4,22%</t>
+          <t>4,42%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>9,52%</t>
+          <t>9,41%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6454,12 +6454,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>22982</t>
+          <t>23085</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>46059</t>
+          <t>45471</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6469,12 +6469,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>7,06%</t>
+          <t>7,09%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>14,15%</t>
+          <t>13,97%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6489,12 +6489,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>45622</t>
+          <t>46434</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>74219</t>
+          <t>76505</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6504,12 +6504,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>6,28%</t>
+          <t>6,39%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>10,21%</t>
+          <t>10,53%</t>
         </is>
       </c>
     </row>
@@ -6532,12 +6532,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>23175</t>
+          <t>22395</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>44534</t>
+          <t>44652</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6547,12 +6547,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>5,78%</t>
+          <t>5,58%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>11,1%</t>
+          <t>11,13%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6567,12 +6567,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>20256</t>
+          <t>21536</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>42053</t>
+          <t>42315</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6582,12 +6582,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>6,22%</t>
+          <t>6,62%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>12,92%</t>
+          <t>13,0%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6602,12 +6602,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>50213</t>
+          <t>49251</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>81477</t>
+          <t>80392</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6617,12 +6617,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>6,91%</t>
+          <t>6,78%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>11,21%</t>
+          <t>11,06%</t>
         </is>
       </c>
     </row>
@@ -6645,12 +6645,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>58978</t>
+          <t>59950</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>91902</t>
+          <t>91351</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -6660,12 +6660,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>14,7%</t>
+          <t>14,94%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>22,91%</t>
+          <t>22,77%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -6680,12 +6680,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>39000</t>
+          <t>39052</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>66877</t>
+          <t>66678</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6695,12 +6695,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>11,98%</t>
+          <t>12,0%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>20,55%</t>
+          <t>20,49%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6715,12 +6715,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>105877</t>
+          <t>108569</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>149546</t>
+          <t>148472</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6730,12 +6730,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>14,57%</t>
+          <t>14,94%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>20,58%</t>
+          <t>20,43%</t>
         </is>
       </c>
     </row>
@@ -6758,12 +6758,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>88149</t>
+          <t>86327</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>124157</t>
+          <t>120796</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6773,12 +6773,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>21,97%</t>
+          <t>21,52%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>30,95%</t>
+          <t>30,11%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6793,12 +6793,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>74028</t>
+          <t>73749</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>106329</t>
+          <t>106247</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6808,12 +6808,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>22,74%</t>
+          <t>22,66%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>32,67%</t>
+          <t>32,64%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6828,12 +6828,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>170721</t>
+          <t>169281</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>219968</t>
+          <t>219557</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6843,12 +6843,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>23,49%</t>
+          <t>23,3%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>30,27%</t>
+          <t>30,22%</t>
         </is>
       </c>
     </row>
@@ -6871,12 +6871,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>145840</t>
+          <t>143575</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>183577</t>
+          <t>182862</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6886,12 +6886,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>36,35%</t>
+          <t>35,79%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>45,76%</t>
+          <t>45,58%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6906,12 +6906,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>103323</t>
+          <t>102241</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>139007</t>
+          <t>138003</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6921,12 +6921,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>31,75%</t>
+          <t>31,41%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>42,71%</t>
+          <t>42,4%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6941,12 +6941,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>257465</t>
+          <t>255997</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>308331</t>
+          <t>309822</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6956,12 +6956,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>35,43%</t>
+          <t>35,23%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>42,43%</t>
+          <t>42,64%</t>
         </is>
       </c>
     </row>
@@ -7101,12 +7101,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>65168</t>
+          <t>63831</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>101431</t>
+          <t>102604</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -7116,12 +7116,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>4,58%</t>
+          <t>4,49%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>7,13%</t>
+          <t>7,21%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -7136,12 +7136,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>73965</t>
+          <t>73450</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>110892</t>
+          <t>109459</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -7151,12 +7151,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>7,13%</t>
+          <t>7,08%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>10,69%</t>
+          <t>10,55%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -7171,12 +7171,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>146978</t>
+          <t>148285</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>199217</t>
+          <t>196159</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -7186,12 +7186,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>5,98%</t>
+          <t>6,03%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>8,1%</t>
+          <t>7,98%</t>
         </is>
       </c>
     </row>
@@ -7214,12 +7214,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>116073</t>
+          <t>116065</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>162466</t>
+          <t>161761</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -7234,7 +7234,7 @@
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>11,42%</t>
+          <t>11,37%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7249,12 +7249,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>106431</t>
+          <t>108633</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>148650</t>
+          <t>150378</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>10,26%</t>
+          <t>10,47%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>14,33%</t>
+          <t>14,5%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -7284,12 +7284,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>237554</t>
+          <t>232820</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>300488</t>
+          <t>296757</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -7299,12 +7299,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>9,66%</t>
+          <t>9,47%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>12,22%</t>
+          <t>12,07%</t>
         </is>
       </c>
     </row>
@@ -7327,12 +7327,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>327380</t>
+          <t>325332</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>391865</t>
+          <t>393512</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -7342,12 +7342,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>23,02%</t>
+          <t>22,87%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>27,55%</t>
+          <t>27,67%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -7362,12 +7362,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>202857</t>
+          <t>205956</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>259802</t>
+          <t>261059</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -7377,12 +7377,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>19,56%</t>
+          <t>19,86%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>25,05%</t>
+          <t>25,17%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -7397,12 +7397,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>546345</t>
+          <t>543659</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>632491</t>
+          <t>633200</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -7412,12 +7412,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>22,21%</t>
+          <t>22,1%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>25,72%</t>
+          <t>25,75%</t>
         </is>
       </c>
     </row>
@@ -7440,12 +7440,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>327511</t>
+          <t>332091</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>397596</t>
+          <t>397521</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -7455,7 +7455,7 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>23,03%</t>
+          <t>23,35%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
@@ -7475,12 +7475,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>245695</t>
+          <t>248417</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>302439</t>
+          <t>303396</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -7490,12 +7490,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>23,69%</t>
+          <t>23,95%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>29,16%</t>
+          <t>29,25%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -7510,12 +7510,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>593072</t>
+          <t>596597</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>682836</t>
+          <t>685202</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -7525,12 +7525,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>24,11%</t>
+          <t>24,26%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>27,76%</t>
+          <t>27,86%</t>
         </is>
       </c>
     </row>
@@ -7553,12 +7553,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>444873</t>
+          <t>447229</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>518906</t>
+          <t>520952</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -7568,12 +7568,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>31,28%</t>
+          <t>31,44%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>36,48%</t>
+          <t>36,63%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -7588,12 +7588,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>287597</t>
+          <t>283995</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>344681</t>
+          <t>342580</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -7603,12 +7603,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>27,73%</t>
+          <t>27,38%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>33,23%</t>
+          <t>33,03%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -7623,12 +7623,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>749019</t>
+          <t>749016</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>844109</t>
+          <t>844967</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -7643,7 +7643,7 @@
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>34,32%</t>
+          <t>34,36%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P6713-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P6713-Habitat-trans_orig.xlsx
@@ -731,12 +731,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1047</t>
+          <t>1043</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>10187</t>
+          <t>9401</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -751,7 +751,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,79%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -766,12 +766,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>2887</t>
+          <t>2903</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>12712</t>
+          <t>12924</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -781,12 +781,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>7,88%</t>
+          <t>8,01%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -801,12 +801,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>5839</t>
+          <t>5906</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>18639</t>
+          <t>18637</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -816,7 +816,7 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
@@ -844,12 +844,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>7774</t>
+          <t>7451</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>25274</t>
+          <t>24263</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -859,12 +859,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>2,77%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>9,4%</t>
+          <t>9,02%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -879,12 +879,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>4233</t>
+          <t>3898</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>17131</t>
+          <t>16844</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -894,12 +894,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>2,42%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>10,62%</t>
+          <t>10,44%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -914,12 +914,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>14902</t>
+          <t>14811</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>36983</t>
+          <t>35648</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -929,12 +929,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>3,44%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>8,6%</t>
+          <t>8,29%</t>
         </is>
       </c>
     </row>
@@ -957,12 +957,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>37451</t>
+          <t>36745</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>61871</t>
+          <t>61832</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -972,12 +972,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>13,93%</t>
+          <t>13,66%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>23,01%</t>
+          <t>22,99%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>25423</t>
+          <t>24871</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>47136</t>
+          <t>47019</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>15,76%</t>
+          <t>15,42%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>29,23%</t>
+          <t>29,15%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>68494</t>
+          <t>67830</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>102594</t>
+          <t>100926</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1042,12 +1042,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>15,92%</t>
+          <t>15,77%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>23,85%</t>
+          <t>23,46%</t>
         </is>
       </c>
     </row>
@@ -1070,12 +1070,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>48611</t>
+          <t>49743</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>77376</t>
+          <t>75926</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1085,12 +1085,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>18,08%</t>
+          <t>18,5%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>28,77%</t>
+          <t>28,23%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1105,12 +1105,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>33638</t>
+          <t>33066</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>56868</t>
+          <t>57234</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1120,12 +1120,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>20,86%</t>
+          <t>20,5%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>35,26%</t>
+          <t>35,49%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1140,12 +1140,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>87754</t>
+          <t>88333</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>124750</t>
+          <t>124388</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1155,12 +1155,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>20,4%</t>
+          <t>20,53%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>29,0%</t>
+          <t>28,91%</t>
         </is>
       </c>
     </row>
@@ -1183,12 +1183,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>122223</t>
+          <t>123579</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>156273</t>
+          <t>156760</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1198,12 +1198,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>45,45%</t>
+          <t>45,95%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>58,11%</t>
+          <t>58,29%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1218,12 +1218,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>52198</t>
+          <t>52834</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>78180</t>
+          <t>78889</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1233,12 +1233,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>32,37%</t>
+          <t>32,76%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>48,48%</t>
+          <t>48,92%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1253,12 +1253,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>185526</t>
+          <t>186381</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>227004</t>
+          <t>225953</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1268,12 +1268,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>43,12%</t>
+          <t>43,32%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>52,77%</t>
+          <t>52,52%</t>
         </is>
       </c>
     </row>
@@ -1413,12 +1413,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>14107</t>
+          <t>13444</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>33678</t>
+          <t>33500</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1428,12 +1428,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>3,29%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>8,24%</t>
+          <t>8,2%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1448,12 +1448,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>11470</t>
+          <t>11336</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>28521</t>
+          <t>27953</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1463,12 +1463,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>4,26%</t>
+          <t>4,21%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>10,6%</t>
+          <t>10,38%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1483,12 +1483,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>30024</t>
+          <t>29295</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>55202</t>
+          <t>55468</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1498,12 +1498,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,43%</t>
+          <t>4,32%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>8,14%</t>
+          <t>8,18%</t>
         </is>
       </c>
     </row>
@@ -1526,12 +1526,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>14977</t>
+          <t>14942</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>36179</t>
+          <t>33886</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1541,12 +1541,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>3,66%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>8,85%</t>
+          <t>8,29%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1561,12 +1561,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>13235</t>
+          <t>14091</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>30520</t>
+          <t>31318</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1576,12 +1576,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>4,92%</t>
+          <t>5,23%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>11,34%</t>
+          <t>11,63%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1596,12 +1596,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>32577</t>
+          <t>32728</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>59753</t>
+          <t>60053</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1611,12 +1611,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>4,81%</t>
+          <t>4,83%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>8,82%</t>
+          <t>8,86%</t>
         </is>
       </c>
     </row>
@@ -1639,12 +1639,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>62629</t>
+          <t>63993</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>94079</t>
+          <t>97169</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1654,12 +1654,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>15,33%</t>
+          <t>15,66%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>23,02%</t>
+          <t>23,78%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1674,12 +1674,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>40802</t>
+          <t>41610</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>68357</t>
+          <t>69611</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1689,12 +1689,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>15,16%</t>
+          <t>15,46%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>25,39%</t>
+          <t>25,86%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1709,12 +1709,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>112619</t>
+          <t>111324</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>153365</t>
+          <t>152385</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1724,12 +1724,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>16,62%</t>
+          <t>16,42%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>22,63%</t>
+          <t>22,48%</t>
         </is>
       </c>
     </row>
@@ -1752,12 +1752,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>77480</t>
+          <t>76161</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>114153</t>
+          <t>113839</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1767,12 +1767,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>18,96%</t>
+          <t>18,64%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>27,94%</t>
+          <t>27,86%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1787,12 +1787,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>44896</t>
+          <t>44053</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>72596</t>
+          <t>71280</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1802,12 +1802,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>16,68%</t>
+          <t>16,37%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>26,97%</t>
+          <t>26,48%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1822,12 +1822,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>131541</t>
+          <t>130420</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>176419</t>
+          <t>176914</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1837,12 +1837,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>19,41%</t>
+          <t>19,24%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>26,03%</t>
+          <t>26,1%</t>
         </is>
       </c>
     </row>
@@ -1865,12 +1865,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>170410</t>
+          <t>170629</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>212874</t>
+          <t>212708</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1880,12 +1880,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>41,71%</t>
+          <t>41,76%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>52,1%</t>
+          <t>52,06%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1900,12 +1900,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>100916</t>
+          <t>100785</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>133161</t>
+          <t>135585</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1915,12 +1915,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>37,49%</t>
+          <t>37,44%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>49,47%</t>
+          <t>50,37%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1935,12 +1935,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>282329</t>
+          <t>281169</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>335263</t>
+          <t>335431</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1950,12 +1950,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>41,65%</t>
+          <t>41,48%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>49,46%</t>
+          <t>49,49%</t>
         </is>
       </c>
     </row>
@@ -2095,12 +2095,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>7053</t>
+          <t>7105</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>21908</t>
+          <t>22161</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2110,12 +2110,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>6,84%</t>
+          <t>6,91%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2130,12 +2130,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>12328</t>
+          <t>12180</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>31929</t>
+          <t>32386</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2145,12 +2145,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>5,78%</t>
+          <t>5,71%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>14,97%</t>
+          <t>15,18%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2165,12 +2165,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>23611</t>
+          <t>23949</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>48054</t>
+          <t>49257</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>4,42%</t>
+          <t>4,49%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>9,0%</t>
+          <t>9,23%</t>
         </is>
       </c>
     </row>
@@ -2208,12 +2208,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>13196</t>
+          <t>13982</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>33067</t>
+          <t>32683</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2223,12 +2223,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>4,12%</t>
+          <t>4,36%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>10,32%</t>
+          <t>10,2%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2248,7 +2248,7 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>24183</t>
+          <t>24077</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2263,7 +2263,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>11,33%</t>
+          <t>11,29%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2278,12 +2278,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>24216</t>
+          <t>24580</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>50415</t>
+          <t>49226</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2293,12 +2293,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>4,54%</t>
+          <t>4,6%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>9,44%</t>
+          <t>9,22%</t>
         </is>
       </c>
     </row>
@@ -2321,12 +2321,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>53340</t>
+          <t>52718</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>84155</t>
+          <t>83532</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2336,12 +2336,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>16,64%</t>
+          <t>16,45%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>26,26%</t>
+          <t>26,06%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2356,12 +2356,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>29819</t>
+          <t>30280</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>55087</t>
+          <t>55704</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2371,12 +2371,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>13,98%</t>
+          <t>14,19%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>25,82%</t>
+          <t>26,11%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2391,12 +2391,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>91182</t>
+          <t>90691</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>129580</t>
+          <t>130645</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2406,12 +2406,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>17,08%</t>
+          <t>16,99%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>24,27%</t>
+          <t>24,47%</t>
         </is>
       </c>
     </row>
@@ -2434,12 +2434,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>39398</t>
+          <t>39862</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>67524</t>
+          <t>67866</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>12,29%</t>
+          <t>12,44%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>21,07%</t>
+          <t>21,18%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2469,12 +2469,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>23771</t>
+          <t>22918</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>46413</t>
+          <t>45967</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2484,12 +2484,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>11,14%</t>
+          <t>10,74%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>21,75%</t>
+          <t>21,55%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2504,12 +2504,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>69626</t>
+          <t>70347</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>106098</t>
+          <t>105914</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2519,12 +2519,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>13,04%</t>
+          <t>13,18%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>19,87%</t>
+          <t>19,84%</t>
         </is>
       </c>
     </row>
@@ -2547,12 +2547,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>147223</t>
+          <t>147078</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>183461</t>
+          <t>183950</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2562,12 +2562,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>45,94%</t>
+          <t>45,89%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>57,25%</t>
+          <t>57,4%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2582,12 +2582,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>86820</t>
+          <t>87377</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>116044</t>
+          <t>118682</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2597,12 +2597,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>40,69%</t>
+          <t>40,95%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>54,39%</t>
+          <t>55,63%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2617,12 +2617,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>241760</t>
+          <t>244107</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>293405</t>
+          <t>292786</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2632,12 +2632,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>45,29%</t>
+          <t>45,73%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>54,96%</t>
+          <t>54,85%</t>
         </is>
       </c>
     </row>
@@ -2777,12 +2777,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>12193</t>
+          <t>12202</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>29747</t>
+          <t>31034</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2797,7 +2797,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>7,14%</t>
+          <t>7,45%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2812,12 +2812,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>8075</t>
+          <t>8094</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>22253</t>
+          <t>22626</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2832,7 +2832,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>7,41%</t>
+          <t>7,53%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2847,12 +2847,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>23580</t>
+          <t>23919</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>48191</t>
+          <t>48910</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>3,34%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>6,72%</t>
+          <t>6,82%</t>
         </is>
       </c>
     </row>
@@ -2890,12 +2890,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>9984</t>
+          <t>9851</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>26849</t>
+          <t>27193</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2905,12 +2905,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,37%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>6,45%</t>
+          <t>6,53%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2925,12 +2925,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>11278</t>
+          <t>11206</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>28923</t>
+          <t>29744</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2940,12 +2940,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>3,73%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>9,63%</t>
+          <t>9,9%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2960,12 +2960,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>24567</t>
+          <t>24056</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>48929</t>
+          <t>48861</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2975,12 +2975,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>3,36%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>6,83%</t>
+          <t>6,82%</t>
         </is>
       </c>
     </row>
@@ -3003,12 +3003,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>79120</t>
+          <t>78328</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>113734</t>
+          <t>113681</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3018,12 +3018,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>19,0%</t>
+          <t>18,81%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>27,31%</t>
+          <t>27,3%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3038,12 +3038,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>52730</t>
+          <t>53753</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>82479</t>
+          <t>84476</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3053,12 +3053,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>17,55%</t>
+          <t>17,89%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>27,45%</t>
+          <t>28,12%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3073,12 +3073,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>138099</t>
+          <t>139593</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>184973</t>
+          <t>187693</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3088,12 +3088,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>19,26%</t>
+          <t>19,47%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>25,8%</t>
+          <t>26,18%</t>
         </is>
       </c>
     </row>
@@ -3116,12 +3116,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>98364</t>
+          <t>97876</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>135511</t>
+          <t>135189</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3131,12 +3131,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>23,62%</t>
+          <t>23,5%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>32,54%</t>
+          <t>32,46%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3151,12 +3151,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>50075</t>
+          <t>50224</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>80689</t>
+          <t>78120</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3166,12 +3166,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>16,67%</t>
+          <t>16,72%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>26,86%</t>
+          <t>26,0%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3186,12 +3186,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>157566</t>
+          <t>155520</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>204564</t>
+          <t>202967</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3201,12 +3201,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>21,98%</t>
+          <t>21,69%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>28,54%</t>
+          <t>28,31%</t>
         </is>
       </c>
     </row>
@@ -3229,12 +3229,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>149311</t>
+          <t>149143</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>190893</t>
+          <t>190715</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3244,12 +3244,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>35,86%</t>
+          <t>35,82%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>45,84%</t>
+          <t>45,8%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3264,12 +3264,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>120414</t>
+          <t>119786</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>155817</t>
+          <t>154872</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3279,12 +3279,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>40,08%</t>
+          <t>39,87%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>51,86%</t>
+          <t>51,55%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3299,12 +3299,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>282097</t>
+          <t>278311</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>332850</t>
+          <t>335487</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3314,12 +3314,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>39,35%</t>
+          <t>38,82%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>46,43%</t>
+          <t>46,8%</t>
         </is>
       </c>
     </row>
@@ -3459,12 +3459,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>44843</t>
+          <t>45365</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>76887</t>
+          <t>76903</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3474,7 +3474,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>3,21%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -3494,12 +3494,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>46453</t>
+          <t>45423</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>76194</t>
+          <t>77776</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3509,12 +3509,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>4,92%</t>
+          <t>4,81%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>8,07%</t>
+          <t>8,24%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3529,12 +3529,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>96706</t>
+          <t>99184</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>139908</t>
+          <t>143265</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3544,12 +3544,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>4,21%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>5,93%</t>
+          <t>6,07%</t>
         </is>
       </c>
     </row>
@@ -3572,12 +3572,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>59406</t>
+          <t>59952</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>95850</t>
+          <t>95520</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3587,12 +3587,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>4,24%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>6,78%</t>
+          <t>6,75%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3607,12 +3607,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>49205</t>
+          <t>48629</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>80445</t>
+          <t>82204</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3622,12 +3622,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>5,21%</t>
+          <t>5,15%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>8,52%</t>
+          <t>8,71%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3642,12 +3642,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>114879</t>
+          <t>116201</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>164835</t>
+          <t>165514</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3657,12 +3657,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>4,87%</t>
+          <t>4,93%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>6,99%</t>
+          <t>7,02%</t>
         </is>
       </c>
     </row>
@@ -3685,12 +3685,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>259390</t>
+          <t>257683</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>319812</t>
+          <t>321132</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3700,12 +3700,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>18,34%</t>
+          <t>18,22%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>22,61%</t>
+          <t>22,7%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3720,12 +3720,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>173678</t>
+          <t>174840</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>224700</t>
+          <t>227362</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3735,12 +3735,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>18,39%</t>
+          <t>18,52%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>23,8%</t>
+          <t>24,08%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3755,12 +3755,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>449396</t>
+          <t>443412</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>530917</t>
+          <t>529327</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3770,12 +3770,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>19,05%</t>
+          <t>18,8%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>22,51%</t>
+          <t>22,44%</t>
         </is>
       </c>
     </row>
@@ -3798,12 +3798,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>290681</t>
+          <t>293432</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>357649</t>
+          <t>356761</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3813,12 +3813,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>20,55%</t>
+          <t>20,75%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>25,29%</t>
+          <t>25,22%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3833,12 +3833,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>173052</t>
+          <t>174130</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>226030</t>
+          <t>225532</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3848,12 +3848,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>18,33%</t>
+          <t>18,44%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>23,94%</t>
+          <t>23,88%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3868,12 +3868,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>482769</t>
+          <t>483511</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>562307</t>
+          <t>568824</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3883,12 +3883,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>20,47%</t>
+          <t>20,5%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>23,84%</t>
+          <t>24,12%</t>
         </is>
       </c>
     </row>
@@ -3911,12 +3911,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>629882</t>
+          <t>623768</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>707062</t>
+          <t>701651</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3926,12 +3926,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>44,53%</t>
+          <t>44,1%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>49,99%</t>
+          <t>49,61%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3946,12 +3946,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>392031</t>
+          <t>391152</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>455033</t>
+          <t>453425</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3961,12 +3961,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>41,52%</t>
+          <t>41,42%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>48,19%</t>
+          <t>48,02%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3981,12 +3981,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>1040461</t>
+          <t>1032744</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>1144728</t>
+          <t>1139157</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3996,12 +3996,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>44,11%</t>
+          <t>43,78%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>48,53%</t>
+          <t>48,3%</t>
         </is>
       </c>
     </row>
@@ -4373,12 +4373,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>8953</t>
+          <t>8496</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>24515</t>
+          <t>24037</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4388,12 +4388,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>3,49%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>10,08%</t>
+          <t>9,88%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4408,12 +4408,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>10835</t>
+          <t>11116</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>26848</t>
+          <t>26989</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4423,12 +4423,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>6,47%</t>
+          <t>6,64%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>16,04%</t>
+          <t>16,13%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4443,12 +4443,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>21432</t>
+          <t>23643</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>44148</t>
+          <t>45962</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4458,12 +4458,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>5,22%</t>
+          <t>5,76%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>10,75%</t>
+          <t>11,19%</t>
         </is>
       </c>
     </row>
@@ -4486,12 +4486,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>21451</t>
+          <t>20802</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>41757</t>
+          <t>42318</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4501,12 +4501,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>8,82%</t>
+          <t>8,55%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>17,16%</t>
+          <t>17,39%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4521,12 +4521,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>20007</t>
+          <t>21002</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>40395</t>
+          <t>39196</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4536,12 +4536,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>11,95%</t>
+          <t>12,55%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>24,14%</t>
+          <t>23,42%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4556,12 +4556,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>46237</t>
+          <t>47851</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>76409</t>
+          <t>76462</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4571,12 +4571,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>11,26%</t>
+          <t>11,65%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>18,61%</t>
+          <t>18,62%</t>
         </is>
       </c>
     </row>
@@ -4599,12 +4599,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>47138</t>
+          <t>47047</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>74420</t>
+          <t>73839</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4614,12 +4614,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>19,38%</t>
+          <t>19,34%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>30,59%</t>
+          <t>30,35%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -4634,12 +4634,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>23931</t>
+          <t>23716</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>42958</t>
+          <t>42284</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4649,12 +4649,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
+          <t>14,17%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>25,67%</t>
+          <t>25,26%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -4669,12 +4669,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>78388</t>
+          <t>76002</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>109687</t>
+          <t>110450</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4684,12 +4684,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>19,09%</t>
+          <t>18,51%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>26,71%</t>
+          <t>26,9%</t>
         </is>
       </c>
     </row>
@@ -4712,12 +4712,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>47680</t>
+          <t>47661</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>75077</t>
+          <t>75626</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4727,12 +4727,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>19,6%</t>
+          <t>19,59%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>30,86%</t>
+          <t>31,08%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4747,12 +4747,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>37068</t>
+          <t>37439</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>60355</t>
+          <t>59981</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4762,12 +4762,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>22,15%</t>
+          <t>22,37%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>36,06%</t>
+          <t>35,84%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4782,7 +4782,7 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>91914</t>
+          <t>91749</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
@@ -4797,7 +4797,7 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>22,38%</t>
+          <t>22,34%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>63137</t>
+          <t>63373</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>92317</t>
+          <t>92818</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4840,12 +4840,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>25,95%</t>
+          <t>26,05%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>37,95%</t>
+          <t>38,15%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4860,12 +4860,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>29326</t>
+          <t>28786</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>51855</t>
+          <t>49282</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4875,12 +4875,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>17,52%</t>
+          <t>17,2%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>30,98%</t>
+          <t>29,45%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4895,12 +4895,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>98394</t>
+          <t>98457</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>135133</t>
+          <t>135089</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4910,12 +4910,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>23,96%</t>
+          <t>23,98%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>32,91%</t>
+          <t>32,9%</t>
         </is>
       </c>
     </row>
@@ -5055,12 +5055,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>8755</t>
+          <t>8956</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>25881</t>
+          <t>25211</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5070,12 +5070,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>6,25%</t>
+          <t>6,09%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5090,12 +5090,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>14402</t>
+          <t>14129</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>33870</t>
+          <t>32687</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5105,12 +5105,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>5,26%</t>
+          <t>5,16%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>12,37%</t>
+          <t>11,94%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5125,12 +5125,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>26645</t>
+          <t>27054</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>51844</t>
+          <t>52206</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5140,12 +5140,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,87%</t>
+          <t>3,93%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>7,54%</t>
+          <t>7,59%</t>
         </is>
       </c>
     </row>
@@ -5168,12 +5168,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>23047</t>
+          <t>22816</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>45633</t>
+          <t>45935</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5183,12 +5183,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>5,57%</t>
+          <t>5,51%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>11,02%</t>
+          <t>11,09%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5203,12 +5203,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>21289</t>
+          <t>22238</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>42402</t>
+          <t>42258</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5218,12 +5218,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>7,78%</t>
+          <t>8,12%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>15,49%</t>
+          <t>15,44%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5238,12 +5238,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>51252</t>
+          <t>50753</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>82266</t>
+          <t>81011</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5253,12 +5253,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>7,45%</t>
+          <t>7,38%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>11,96%</t>
+          <t>11,78%</t>
         </is>
       </c>
     </row>
@@ -5281,12 +5281,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>87652</t>
+          <t>89620</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>125628</t>
+          <t>125493</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5296,12 +5296,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>21,17%</t>
+          <t>21,65%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>30,34%</t>
+          <t>30,31%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5316,12 +5316,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>47567</t>
+          <t>48374</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>75429</t>
+          <t>77220</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5331,12 +5331,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>17,37%</t>
+          <t>17,67%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>27,55%</t>
+          <t>28,21%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -5351,12 +5351,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>145859</t>
+          <t>145368</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>193565</t>
+          <t>192460</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5366,12 +5366,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>21,21%</t>
+          <t>21,13%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>28,14%</t>
+          <t>27,98%</t>
         </is>
       </c>
     </row>
@@ -5394,12 +5394,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>100646</t>
+          <t>102648</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>140855</t>
+          <t>143464</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5409,12 +5409,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>24,31%</t>
+          <t>24,79%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>34,02%</t>
+          <t>34,65%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5429,12 +5429,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>66461</t>
+          <t>64544</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>96740</t>
+          <t>94837</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5444,12 +5444,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>24,28%</t>
+          <t>23,58%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>35,34%</t>
+          <t>34,64%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5464,12 +5464,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>176346</t>
+          <t>177362</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>226903</t>
+          <t>227428</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5479,12 +5479,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>25,64%</t>
+          <t>25,79%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>32,99%</t>
+          <t>33,07%</t>
         </is>
       </c>
     </row>
@@ -5507,12 +5507,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>119261</t>
+          <t>119927</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>159295</t>
+          <t>160156</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5522,12 +5522,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>28,8%</t>
+          <t>28,97%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>38,47%</t>
+          <t>38,68%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5542,12 +5542,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>63371</t>
+          <t>65571</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>94874</t>
+          <t>95766</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5557,12 +5557,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>23,15%</t>
+          <t>23,95%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>34,65%</t>
+          <t>34,98%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5577,12 +5577,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>192186</t>
+          <t>192380</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>241877</t>
+          <t>242900</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5592,12 +5592,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>27,94%</t>
+          <t>27,97%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>35,17%</t>
+          <t>35,31%</t>
         </is>
       </c>
     </row>
@@ -5737,12 +5737,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>16102</t>
+          <t>15250</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>34982</t>
+          <t>35612</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5752,12 +5752,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>4,43%</t>
+          <t>4,19%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>9,62%</t>
+          <t>9,79%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5772,12 +5772,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>10506</t>
+          <t>9802</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>27592</t>
+          <t>27083</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5787,12 +5787,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>3,62%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>10,2%</t>
+          <t>10,01%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5807,12 +5807,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>28979</t>
+          <t>30552</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>56522</t>
+          <t>56612</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5822,12 +5822,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>4,57%</t>
+          <t>4,82%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>8,91%</t>
+          <t>8,92%</t>
         </is>
       </c>
     </row>
@@ -5850,12 +5850,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>29382</t>
+          <t>29919</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>55072</t>
+          <t>55585</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5865,12 +5865,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>8,08%</t>
+          <t>8,22%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>15,14%</t>
+          <t>15,28%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>26099</t>
+          <t>26791</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>48920</t>
+          <t>47943</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5900,12 +5900,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>9,65%</t>
+          <t>9,9%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>18,08%</t>
+          <t>17,72%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5920,12 +5920,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>61198</t>
+          <t>60427</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>95609</t>
+          <t>94519</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5935,12 +5935,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>9,65%</t>
+          <t>9,53%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>15,07%</t>
+          <t>14,9%</t>
         </is>
       </c>
     </row>
@@ -5963,12 +5963,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>97295</t>
+          <t>97686</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>135516</t>
+          <t>136456</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5978,12 +5978,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>26,74%</t>
+          <t>26,85%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>37,25%</t>
+          <t>37,51%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -5998,12 +5998,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>70743</t>
+          <t>70437</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>102051</t>
+          <t>100430</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6013,12 +6013,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>26,15%</t>
+          <t>26,03%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>37,72%</t>
+          <t>37,12%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>177654</t>
+          <t>176886</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>226897</t>
+          <t>225525</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6048,12 +6048,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>28,0%</t>
+          <t>27,88%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>35,77%</t>
+          <t>35,55%</t>
         </is>
       </c>
     </row>
@@ -6076,12 +6076,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>62151</t>
+          <t>62813</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>94798</t>
+          <t>96076</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -6091,12 +6091,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>17,08%</t>
+          <t>17,26%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>26,06%</t>
+          <t>26,41%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -6111,12 +6111,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>44872</t>
+          <t>45437</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>71022</t>
+          <t>71306</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -6126,12 +6126,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>16,58%</t>
+          <t>16,79%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>26,25%</t>
+          <t>26,36%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -6146,12 +6146,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>115257</t>
+          <t>115750</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>156684</t>
+          <t>157019</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -6161,12 +6161,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>18,17%</t>
+          <t>18,25%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>24,7%</t>
+          <t>24,75%</t>
         </is>
       </c>
     </row>
@@ -6189,12 +6189,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>87471</t>
+          <t>87502</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>122796</t>
+          <t>122613</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -6204,12 +6204,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>24,04%</t>
+          <t>24,05%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>33,75%</t>
+          <t>33,7%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -6224,12 +6224,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>59435</t>
+          <t>60743</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>88094</t>
+          <t>91140</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -6239,12 +6239,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>21,97%</t>
+          <t>22,45%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>32,56%</t>
+          <t>33,69%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -6259,12 +6259,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>155971</t>
+          <t>155819</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>202033</t>
+          <t>202692</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6274,12 +6274,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>24,59%</t>
+          <t>24,56%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>31,85%</t>
+          <t>31,95%</t>
         </is>
       </c>
     </row>
@@ -6419,12 +6419,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>17742</t>
+          <t>17374</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>37746</t>
+          <t>36378</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6434,12 +6434,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>4,42%</t>
+          <t>4,33%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>9,41%</t>
+          <t>9,07%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6454,12 +6454,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>23085</t>
+          <t>23335</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>45471</t>
+          <t>46987</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6469,12 +6469,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>7,09%</t>
+          <t>7,17%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>13,97%</t>
+          <t>14,44%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6489,12 +6489,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>46434</t>
+          <t>45827</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>76505</t>
+          <t>75489</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6504,12 +6504,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>6,39%</t>
+          <t>6,31%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>10,53%</t>
+          <t>10,39%</t>
         </is>
       </c>
     </row>
@@ -6532,12 +6532,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>22395</t>
+          <t>21848</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>44652</t>
+          <t>44503</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6547,12 +6547,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>5,58%</t>
+          <t>5,45%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>11,13%</t>
+          <t>11,09%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6567,12 +6567,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>21536</t>
+          <t>20868</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>42315</t>
+          <t>42444</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6582,12 +6582,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>6,62%</t>
+          <t>6,41%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>13,0%</t>
+          <t>13,04%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6602,12 +6602,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>49251</t>
+          <t>48777</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>80392</t>
+          <t>79112</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6617,12 +6617,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>6,78%</t>
+          <t>6,71%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>11,06%</t>
+          <t>10,89%</t>
         </is>
       </c>
     </row>
@@ -6645,12 +6645,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>59950</t>
+          <t>60573</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>91351</t>
+          <t>92785</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -6660,12 +6660,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>14,94%</t>
+          <t>15,1%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>22,77%</t>
+          <t>23,13%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -6680,12 +6680,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>39052</t>
+          <t>38065</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>66678</t>
+          <t>64707</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6695,12 +6695,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>12,0%</t>
+          <t>11,7%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>20,49%</t>
+          <t>19,88%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6715,12 +6715,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>108569</t>
+          <t>106843</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>148472</t>
+          <t>149119</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6730,12 +6730,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>14,94%</t>
+          <t>14,7%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>20,43%</t>
+          <t>20,52%</t>
         </is>
       </c>
     </row>
@@ -6758,12 +6758,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>86327</t>
+          <t>87263</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>120796</t>
+          <t>122491</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6773,12 +6773,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>21,52%</t>
+          <t>21,75%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>30,11%</t>
+          <t>30,53%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6793,12 +6793,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>73749</t>
+          <t>73757</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>106247</t>
+          <t>106654</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6813,7 +6813,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>32,64%</t>
+          <t>32,77%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6828,12 +6828,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>169281</t>
+          <t>168739</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>219557</t>
+          <t>216824</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6843,12 +6843,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>23,3%</t>
+          <t>23,22%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>30,22%</t>
+          <t>29,84%</t>
         </is>
       </c>
     </row>
@@ -6871,12 +6871,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>143575</t>
+          <t>144690</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>182862</t>
+          <t>183956</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6886,12 +6886,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>35,79%</t>
+          <t>36,07%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>45,58%</t>
+          <t>45,85%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6906,12 +6906,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>102241</t>
+          <t>103722</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>138003</t>
+          <t>138039</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6921,12 +6921,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>31,41%</t>
+          <t>31,87%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>42,4%</t>
+          <t>42,41%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6941,12 +6941,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>255997</t>
+          <t>257650</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>309822</t>
+          <t>312903</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6956,12 +6956,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>35,23%</t>
+          <t>35,46%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>42,64%</t>
+          <t>43,06%</t>
         </is>
       </c>
     </row>
@@ -7101,12 +7101,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>63831</t>
+          <t>66025</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>102604</t>
+          <t>101795</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -7116,12 +7116,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>4,49%</t>
+          <t>4,64%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>7,21%</t>
+          <t>7,16%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -7136,12 +7136,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>73450</t>
+          <t>73878</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>109459</t>
+          <t>111489</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -7151,12 +7151,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>7,08%</t>
+          <t>7,12%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>10,55%</t>
+          <t>10,75%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -7171,12 +7171,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>148285</t>
+          <t>147281</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>196159</t>
+          <t>197846</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -7186,12 +7186,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>6,03%</t>
+          <t>5,99%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>7,98%</t>
+          <t>8,04%</t>
         </is>
       </c>
     </row>
@@ -7214,12 +7214,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>116065</t>
+          <t>116574</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>161761</t>
+          <t>159448</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -7229,12 +7229,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>8,16%</t>
+          <t>8,2%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>11,37%</t>
+          <t>11,21%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7249,12 +7249,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>108633</t>
+          <t>107398</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>150378</t>
+          <t>148753</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>10,47%</t>
+          <t>10,35%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>14,5%</t>
+          <t>14,34%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -7284,12 +7284,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>232820</t>
+          <t>234440</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>296757</t>
+          <t>296368</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -7299,12 +7299,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>9,47%</t>
+          <t>9,53%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>12,07%</t>
+          <t>12,05%</t>
         </is>
       </c>
     </row>
@@ -7327,12 +7327,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>325332</t>
+          <t>323701</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>393512</t>
+          <t>388731</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -7342,12 +7342,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>22,87%</t>
+          <t>22,76%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>27,67%</t>
+          <t>27,33%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -7362,12 +7362,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>205956</t>
+          <t>204902</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>261059</t>
+          <t>256757</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -7377,12 +7377,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>19,86%</t>
+          <t>19,76%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>25,17%</t>
+          <t>24,76%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -7397,12 +7397,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>543659</t>
+          <t>548109</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>633200</t>
+          <t>635571</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -7412,12 +7412,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>22,1%</t>
+          <t>22,29%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>25,75%</t>
+          <t>25,84%</t>
         </is>
       </c>
     </row>
@@ -7440,12 +7440,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>332091</t>
+          <t>331235</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>397521</t>
+          <t>398886</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -7455,12 +7455,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>23,35%</t>
+          <t>23,29%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>27,95%</t>
+          <t>28,04%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -7475,12 +7475,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>248417</t>
+          <t>246418</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>303396</t>
+          <t>301678</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -7490,12 +7490,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>23,95%</t>
+          <t>23,76%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>29,25%</t>
+          <t>29,09%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -7510,12 +7510,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>596597</t>
+          <t>593924</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>685202</t>
+          <t>681850</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -7525,12 +7525,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>24,26%</t>
+          <t>24,15%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>27,86%</t>
+          <t>27,72%</t>
         </is>
       </c>
     </row>
@@ -7553,12 +7553,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>447229</t>
+          <t>444076</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>520952</t>
+          <t>517126</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -7568,12 +7568,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>31,44%</t>
+          <t>31,22%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>36,63%</t>
+          <t>36,36%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -7588,12 +7588,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>283995</t>
+          <t>285770</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>342580</t>
+          <t>344400</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -7603,12 +7603,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>27,38%</t>
+          <t>27,55%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>33,03%</t>
+          <t>33,21%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -7623,12 +7623,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>749016</t>
+          <t>748429</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>844967</t>
+          <t>842989</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -7638,12 +7638,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>30,45%</t>
+          <t>30,43%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>34,36%</t>
+          <t>34,27%</t>
         </is>
       </c>
     </row>
